--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Clase-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,97</t>
+          <t>1,28; 4,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,13</t>
+          <t>2,08; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 3,55</t>
+          <t>-3,14; 3,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 7,95</t>
+          <t>1,16; 7,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 3,67</t>
+          <t>0,14; 3,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,42; 5,82</t>
+          <t>2,62; 5,82</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 132,5</t>
+          <t>-51,71; 173,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,5; 373,67</t>
+          <t>17,67; 363,84</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 326,22</t>
+          <t>-1,3; 294,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,04; 525,59</t>
+          <t>84,37; 517,53</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 1,4</t>
+          <t>-2,26; 1,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,63</t>
+          <t>0,03; 4,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,85</t>
+          <t>-4,82; 1,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,19</t>
+          <t>3,13; 10,09</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 0,83</t>
+          <t>-2,55; 0,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,51</t>
+          <t>2,51; 6,3</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,25; 170,55</t>
+          <t>-83,3; 159,9</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,15; 442,05</t>
+          <t>-3,36; 448,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 72,66</t>
+          <t>-73,38; 69,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>46,87; 394,33</t>
+          <t>39,67; 374,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-66,48; 37,96</t>
+          <t>-62,85; 44,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,43; 304,04</t>
+          <t>55,65; 286,5</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,08</t>
+          <t>-4,51; 0,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 5,61</t>
+          <t>-3,49; 5,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 15,89</t>
+          <t>2,09; 15,33</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,62; 17,68</t>
+          <t>6,54; 17,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,73</t>
+          <t>-2,0; 2,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 7,53</t>
+          <t>-2,13; 7,42</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-73,67; 13,87</t>
+          <t>-75,6; 13,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,41; 138,03</t>
+          <t>-60,09; 143,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,24; 342,82</t>
+          <t>20,94; 334,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,94; 436,26</t>
+          <t>65,08; 376,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 67,4</t>
+          <t>-32,48; 67,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,15; 163,35</t>
+          <t>-34,77; 154,62</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; -0,49</t>
+          <t>-3,9; -0,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 6,5</t>
+          <t>2,1; 6,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 2,77</t>
+          <t>-2,25; 2,74</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,13</t>
+          <t>-2,19; 5,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,26</t>
+          <t>-2,62; 0,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,65; 5,3</t>
+          <t>0,16; 5,28</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-57,77; -7,2</t>
+          <t>-58,27; -5,31</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,43; 139,69</t>
+          <t>31,26; 142,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-29,66; 59,66</t>
+          <t>-33,84; 54,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,06; 115,57</t>
+          <t>-27,02; 112,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,1; 6,18</t>
+          <t>-39,32; 5,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,55; 106,23</t>
+          <t>4,88; 102,32</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 4,37</t>
+          <t>-0,48; 4,29</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,79; 8,78</t>
+          <t>2,92; 8,47</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,89</t>
+          <t>-3,95; 2,78</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,66; 12,73</t>
+          <t>2,42; 12,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 2,75</t>
+          <t>-2,31; 2,35</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,69</t>
+          <t>4,33; 10,4</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 178,61</t>
+          <t>-11,42; 172,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>54,82; 368,1</t>
+          <t>58,38; 336,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,39; 26,79</t>
+          <t>-26,86; 26,1</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20,64; 115,42</t>
+          <t>18,56; 113,62</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 35,16</t>
+          <t>-22,62; 30,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,83; 136,5</t>
+          <t>45,71; 134,85</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,82</t>
+          <t>-1,73; 0,83</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 2,5</t>
+          <t>-0,71; 2,44</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 1,32</t>
+          <t>-4,24; 1,54</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,1; 7,28</t>
+          <t>1,46; 7,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 0,98</t>
+          <t>-3,82; 0,97</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,27; 5,37</t>
+          <t>0,52; 5,27</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-73,62; —</t>
+          <t>-81,67; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-31,59; 11,64</t>
+          <t>-30,29; 13,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,23; 63,18</t>
+          <t>9,82; 63,75</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,54; 10,21</t>
+          <t>-32,36; 10,38</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,34; 57,68</t>
+          <t>3,69; 56,51</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,45</t>
+          <t>-1,31; 0,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,22</t>
+          <t>1,29; 4,27</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,95</t>
+          <t>-1,71; 1,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1,78; 6,45</t>
+          <t>2,2; 6,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,46</t>
+          <t>-1,3; 0,45</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,36; 5,09</t>
+          <t>2,43; 5,02</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,4; 15,2</t>
+          <t>-32,62; 12,11</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>43,41; 134,06</t>
+          <t>34,13; 134,3</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-17,55; 11,36</t>
+          <t>-16,92; 12,99</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>17,59; 73,02</t>
+          <t>22,04; 75,23</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,64; 7,54</t>
+          <t>-18,56; 7,67</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>38,55; 84,08</t>
+          <t>36,5; 82,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_Lim_5-Clase-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_Lim_5-Clase-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,44</t>
+          <t>3,64</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,15</t>
+          <t>4,3</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,96</t>
+          <t>1,13; 4,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,26</t>
+          <t>2,26; 5,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,94</t>
+          <t>-2,86; 3,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,54</t>
+          <t>0,9; 7,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,56</t>
+          <t>0,32; 3,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,62; 5,82</t>
+          <t>2,6; 5,92</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1514,18%</t>
+          <t>1604,79%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111,84%</t>
+          <t>113,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>226,87%</t>
+          <t>235,15%</t>
         </is>
       </c>
     </row>
@@ -717,22 +717,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-51,71; 173,51</t>
+          <t>-52,03; 147,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 363,84</t>
+          <t>7,49; 336,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 294,58</t>
+          <t>7,77; 339,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>84,37; 517,53</t>
+          <t>78,19; 541,11</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,4</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,92</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,27</t>
+          <t>-2,33; 1,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,5</t>
+          <t>0,23; 4,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,69</t>
+          <t>-4,31; 1,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,13; 10,09</t>
+          <t>3,31; 10,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 0,97</t>
+          <t>-2,37; 0,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,3</t>
+          <t>2,56; 6,68</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>127,29%</t>
+          <t>121,71%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158,77%</t>
+          <t>158,48%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>150,1%</t>
+          <t>149,9%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-83,3; 159,9</t>
+          <t>-82,25; 177,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 448,69</t>
+          <t>3,71; 436,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-73,38; 69,02</t>
+          <t>-72,97; 64,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,67; 374,31</t>
+          <t>40,31; 380,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 44,27</t>
+          <t>-62,7; 44,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,65; 286,5</t>
+          <t>60,02; 337,07</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>4,23</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,86</t>
+          <t>11,61</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>6,32</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 0,23</t>
+          <t>-4,64; -0,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 5,77</t>
+          <t>0,96; 7,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 15,33</t>
+          <t>1,97; 15,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,54; 17,11</t>
+          <t>5,98; 17,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 2,83</t>
+          <t>-2,03; 2,97</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 7,42</t>
+          <t>3,5; 8,96</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>186,99%</t>
+          <t>183,05%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>123,2%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-75,6; 13,77</t>
+          <t>-73,06; 7,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-60,09; 143,94</t>
+          <t>13,35; 221,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20,94; 334,16</t>
+          <t>14,12; 329,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,08; 376,19</t>
+          <t>70,73; 397,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-32,48; 67,0</t>
+          <t>-34,18; 76,35</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-34,77; 154,62</t>
+          <t>53,54; 226,27</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4,19</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>4,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>4,35</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,9; -0,29</t>
+          <t>-3,65; -0,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,1; 6,47</t>
+          <t>1,73; 6,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,74</t>
+          <t>-2,11; 2,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 5,93</t>
+          <t>2,47; 7,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 0,25</t>
+          <t>-2,66; 0,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,16; 5,28</t>
+          <t>2,78; 6,03</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>75,93%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45,68%</t>
+          <t>83,87%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,27; -5,31</t>
+          <t>-57,05; -7,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>31,26; 142,08</t>
+          <t>25,15; 130,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-33,84; 54,98</t>
+          <t>-29,47; 59,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,02; 112,1</t>
+          <t>32,6; 163,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-39,32; 5,63</t>
+          <t>-41,35; 7,07</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 102,32</t>
+          <t>41,13; 120,64</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8,59</t>
+          <t>10,27</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,9</t>
+          <t>7,91</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 4,29</t>
+          <t>-0,46; 4,2</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,47</t>
+          <t>1,79; 7,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 2,78</t>
+          <t>-4,19; 2,8</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,42; 12,88</t>
+          <t>6,98; 13,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 2,35</t>
+          <t>-2,21; 2,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,4</t>
+          <t>5,49; 10,16</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>159,71%</t>
+          <t>128,99%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,15%</t>
         </is>
       </c>
     </row>
@@ -1331,39 +1331,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 172,12</t>
+          <t>-10,56; 177,14</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>58,38; 336,32</t>
+          <t>29,25; 281,32</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 26,1</t>
+          <t>-28,76; 26,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18,56; 113,62</t>
+          <t>47,39; 125,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-22,62; 30,5</t>
+          <t>-21,93; 29,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,71; 134,85</t>
+          <t>52,15; 130,98</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4,21</t>
+          <t>3,78</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,83</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 0,83</t>
+          <t>-1,5; 0,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 2,44</t>
+          <t>-0,81; 2,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,54</t>
+          <t>-4,75; 1,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,46; 7,25</t>
+          <t>0,96; 6,65</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 0,97</t>
+          <t>-3,71; 0,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,27</t>
+          <t>0,66; 5,27</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>108,74%</t>
+          <t>112,56%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,5%</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-81,67; —</t>
+          <t>-99,81; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-30,29; 13,13</t>
+          <t>-32,38; 12,27</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>9,82; 63,75</t>
+          <t>5,65; 57,53</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-32,36; 10,38</t>
+          <t>-31,33; 11,36</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,69; 56,51</t>
+          <t>5,95; 55,65</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3,11</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>5,82</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,04</t>
+          <t>4,67</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 0,38</t>
+          <t>-1,37; 0,39</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,27</t>
+          <t>2,36; 4,43</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 1,12</t>
+          <t>-1,79; 1,22</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,53</t>
+          <t>4,42; 7,23</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,45</t>
+          <t>-1,17; 0,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,02</t>
+          <t>3,81; 5,57</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>62,65%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>71,97%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 12,11</t>
+          <t>-33,84; 13,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>34,13; 134,3</t>
+          <t>57,75; 140,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-16,92; 12,99</t>
+          <t>-17,92; 14,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22,04; 75,23</t>
+          <t>43,95; 85,93</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-18,56; 7,67</t>
+          <t>-17,05; 8,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>36,5; 82,45</t>
+          <t>54,45; 93,61</t>
         </is>
       </c>
     </row>
